--- a/CEaL_training_material/supplemental_materials/underwater_Piers_map.xlsx
+++ b/CEaL_training_material/supplemental_materials/underwater_Piers_map.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seattle Aquarium Dropbox\Coastal_Climate_Resilience\GitHub\ROV_underwater_wireless_charging\CEaL_training_material\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seattle Aquarium Dropbox\Coastal_Climate_Resilience\GitHub\ROV_underwater_wireless_charging\CEaL_training_material\supplemental_materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CCBD2B-EA73-4D48-8A25-039E80F4A540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F040AB3-A008-49DB-8195-63B3F6A88DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" firstSheet="1" activeTab="1" xr2:uid="{E792B45E-F55D-4DAB-A3F7-EF4D77EFC127}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
   <si>
     <t>PIER 60</t>
   </si>
@@ -134,12 +134,21 @@
   <si>
     <t>Ascent Piling</t>
   </si>
+  <si>
+    <t>Ladder</t>
+  </si>
+  <si>
+    <t>Stop Sign</t>
+  </si>
+  <si>
+    <t>Cement Blocks</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -147,6 +156,7 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="18"/>
@@ -158,6 +168,18 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <name val="Georgia"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -238,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -267,12 +289,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15016,13 +15041,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -15409,13 +15434,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>95249</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -15481,16 +15506,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>36195</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>125730</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>83821</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -15520,8 +15545,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1724025" y="9944100"/>
-          <a:ext cx="342900" cy="371475"/>
+          <a:off x="331470" y="4573905"/>
+          <a:ext cx="354330" cy="360046"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -15680,13 +15705,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -16771,10 +16796,10 @@
         </a:prstGeom>
         <a:pattFill prst="wdDnDiag">
           <a:fgClr>
-            <a:srgbClr val="000000"/>
+            <a:schemeClr val="tx1"/>
           </a:fgClr>
           <a:bgClr>
-            <a:srgbClr val="FFFFFF"/>
+            <a:srgbClr val="FFFF00"/>
           </a:bgClr>
         </a:pattFill>
         <a:ln w="9525">
@@ -20822,55 +20847,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2645" name="Oval 235">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2A7420D-2652-8659-FDD8-DA8BD3486D60}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2171700" y="12001500"/>
-          <a:ext cx="0" cy="66675"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="339966" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="57"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>44</xdr:col>
@@ -20949,13 +20925,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>152399</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -21356,60 +21332,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2653" name="Oval 244" descr="Wide downward diagonal">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43163A39-FB9B-DF64-7761-9F678DB55ED3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1781175" y="11363325"/>
-          <a:ext cx="95250" cy="95250"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:pattFill prst="wdDnDiag">
-          <a:fgClr>
-            <a:srgbClr val="000000"/>
-          </a:fgClr>
-          <a:bgClr>
-            <a:srgbClr val="FFFFFF"/>
-          </a:bgClr>
-        </a:pattFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-          </a:solidFill>
-          <a:round/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>35</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>64</xdr:row>
@@ -22466,15 +22388,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>124557</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>124557</xdr:rowOff>
+      <xdr:colOff>113127</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>120747</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>43961</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>14654</xdr:rowOff>
+      <xdr:colOff>32531</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>10844</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -22489,8 +22411,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1773115" y="8814288"/>
-          <a:ext cx="102577" cy="212481"/>
+          <a:off x="486507" y="3252567"/>
+          <a:ext cx="106094" cy="202517"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22590,13 +22512,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>73269</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>21980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>102577</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>124557</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -22611,9 +22533,9 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="17559226">
-          <a:off x="1776779" y="8495566"/>
-          <a:ext cx="102577" cy="212481"/>
+        <a:xfrm rot="16200000">
+          <a:off x="503359" y="3097090"/>
+          <a:ext cx="102577" cy="215998"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22646,6 +22568,196 @@
           <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
         </a:p>
       </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>102577</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>105801</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>183173</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>879</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA697AA9-5184-4742-BD44-B8EF32F63E00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7196797" y="4799721"/>
+          <a:ext cx="80596" cy="207498"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="wdDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="tx1"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFF00"/>
+          </a:bgClr>
+        </a:pattFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>140677</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>143901</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>34583</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38979</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABFDEA49-D127-420D-8F12-653DAF256DCE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="514057" y="3588141"/>
+          <a:ext cx="80596" cy="207498"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="wdDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="tx1"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFF00"/>
+          </a:bgClr>
+        </a:pattFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100" kern="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1905</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Oval 142" descr="Wide downward diagonal">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC968F56-48A0-4E7A-B4F6-5DE652F97E26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="468630" y="5949315"/>
+          <a:ext cx="177165" cy="156210"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:pattFill prst="wdDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="tx1"/>
+          </a:fgClr>
+          <a:bgClr>
+            <a:srgbClr val="FFFF00"/>
+          </a:bgClr>
+        </a:pattFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -23790,22 +23902,22 @@
       <c r="AA80" s="15"/>
       <c r="AB80" s="14"/>
       <c r="AC80" s="14"/>
-      <c r="AD80" s="18">
+      <c r="AD80" s="19">
         <v>40</v>
       </c>
-      <c r="AE80" s="18"/>
+      <c r="AE80" s="19"/>
       <c r="AF80" s="14"/>
       <c r="AG80" s="14"/>
-      <c r="AH80" s="18">
+      <c r="AH80" s="19">
         <v>60</v>
       </c>
-      <c r="AI80" s="18"/>
+      <c r="AI80" s="19"/>
       <c r="AJ80" s="14"/>
       <c r="AK80" s="14"/>
-      <c r="AL80" s="18">
+      <c r="AL80" s="19">
         <v>80</v>
       </c>
-      <c r="AM80" s="18"/>
+      <c r="AM80" s="19"/>
     </row>
     <row r="81" spans="11:38" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="K81" t="s">
@@ -24017,6 +24129,21 @@
       <c r="BF15" s="2"/>
     </row>
     <row r="16" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
       <c r="AL16" s="2"/>
       <c r="AN16" s="2"/>
       <c r="AO16" s="2"/>
@@ -24038,7 +24165,24 @@
       <c r="BE16" s="2"/>
       <c r="BF16" s="2"/>
     </row>
-    <row r="17" spans="3:58" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B17" s="20"/>
+      <c r="C17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
       <c r="AF17" t="s">
         <v>5</v>
       </c>
@@ -24063,10 +24207,24 @@
       <c r="BE17" s="2"/>
       <c r="BF17" s="2"/>
     </row>
-    <row r="18" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="D18" t="s">
-        <v>11</v>
+    <row r="18" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20" t="s">
+        <v>12</v>
       </c>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
       <c r="AL18" s="2"/>
       <c r="AM18">
         <v>32</v>
@@ -24091,10 +24249,22 @@
       <c r="BE18" s="2"/>
       <c r="BF18" s="2"/>
     </row>
-    <row r="19" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="D19" t="s">
-        <v>12</v>
-      </c>
+    <row r="19" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
       <c r="AL19" s="2"/>
       <c r="AN19" s="2"/>
       <c r="AO19" s="2"/>
@@ -24118,8 +24288,24 @@
       <c r="BE19" s="2"/>
       <c r="BF19" s="2"/>
     </row>
-    <row r="20" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="C20" s="6"/>
+    <row r="20" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
       <c r="AL20" s="2"/>
       <c r="AN20" s="2"/>
       <c r="AO20" s="2"/>
@@ -24141,10 +24327,22 @@
       <c r="BE20" s="2"/>
       <c r="BF20" s="2"/>
     </row>
-    <row r="21" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="E21" s="1" t="s">
-        <v>29</v>
-      </c>
+    <row r="21" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
       <c r="AL21">
         <v>34</v>
       </c>
@@ -24170,7 +24368,24 @@
       <c r="BE21" s="2"/>
       <c r="BF21" s="2"/>
     </row>
-    <row r="22" spans="3:58" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
       <c r="AN22" s="2"/>
       <c r="AO22" s="2"/>
       <c r="AP22" s="2"/>
@@ -24191,10 +24406,22 @@
       <c r="BE22" s="2"/>
       <c r="BF22" s="2"/>
     </row>
-    <row r="23" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
+    <row r="23" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
       <c r="AI23">
         <v>35</v>
       </c>
@@ -24220,7 +24447,24 @@
       <c r="BE23" s="2"/>
       <c r="BF23" s="2"/>
     </row>
-    <row r="24" spans="3:58" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
       <c r="AN24" s="2"/>
       <c r="AO24" s="2"/>
       <c r="AP24" s="2"/>
@@ -24241,10 +24485,22 @@
       <c r="BE24" s="2"/>
       <c r="BF24" s="2"/>
     </row>
-    <row r="25" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="E25" t="s">
-        <v>15</v>
-      </c>
+    <row r="25" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
       <c r="AF25" t="s">
         <v>6</v>
       </c>
@@ -24271,7 +24527,24 @@
       <c r="BE25" s="2"/>
       <c r="BF25" s="2"/>
     </row>
-    <row r="26" spans="3:58" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
       <c r="AN26" s="2"/>
       <c r="AO26" s="2"/>
       <c r="AP26" s="2"/>
@@ -24294,10 +24567,22 @@
       <c r="BE26" s="2"/>
       <c r="BF26" s="2"/>
     </row>
-    <row r="27" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="E27" t="s">
-        <v>17</v>
-      </c>
+    <row r="27" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
       <c r="AN27" s="2"/>
       <c r="AO27" s="2"/>
       <c r="AP27" s="2"/>
@@ -24319,7 +24604,24 @@
       <c r="BD27" s="2"/>
       <c r="BE27" s="2"/>
     </row>
-    <row r="28" spans="3:58" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="20"/>
       <c r="AN28" s="2"/>
       <c r="AO28" s="2"/>
       <c r="AP28" s="2"/>
@@ -24340,7 +24642,22 @@
       <c r="BC28" s="2"/>
       <c r="BD28" s="2"/>
     </row>
-    <row r="29" spans="3:58" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
       <c r="AM29">
         <v>42</v>
       </c>
@@ -24360,10 +24677,22 @@
       <c r="BA29" s="2"/>
       <c r="BB29" s="2"/>
     </row>
-    <row r="30" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="F30" t="s">
-        <v>19</v>
-      </c>
+    <row r="30" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="20"/>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
       <c r="AN30" s="2"/>
       <c r="AO30" s="2"/>
       <c r="AP30" s="2"/>
@@ -24382,7 +24711,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="3:58" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
       <c r="AN31" s="2"/>
       <c r="AO31" s="2"/>
       <c r="AP31" s="2"/>
@@ -24396,10 +24741,22 @@
       <c r="AX31" s="2"/>
       <c r="AY31" s="2"/>
     </row>
-    <row r="32" spans="3:58" x14ac:dyDescent="0.4">
-      <c r="AM32">
-        <v>44</v>
-      </c>
+    <row r="32" spans="2:58" x14ac:dyDescent="0.4">
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
       <c r="AN32" s="2"/>
       <c r="AO32" s="2"/>
       <c r="AP32" s="2"/>
@@ -24413,10 +24770,22 @@
       <c r="AX32" s="2"/>
       <c r="AY32" s="2"/>
     </row>
-    <row r="33" spans="4:61" x14ac:dyDescent="0.4">
-      <c r="E33" t="s">
-        <v>20</v>
-      </c>
+    <row r="33" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
       <c r="AN33" s="2"/>
       <c r="AO33" s="2"/>
       <c r="AP33" s="2"/>
@@ -24434,7 +24803,24 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="4:61" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
       <c r="AN34" s="2"/>
       <c r="AO34" s="2"/>
       <c r="AP34" s="2"/>
@@ -24445,7 +24831,22 @@
       <c r="AU34" s="2"/>
       <c r="AV34" s="2"/>
     </row>
-    <row r="35" spans="4:61" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:61" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="20"/>
       <c r="AF35" t="s">
         <v>7</v>
       </c>
@@ -24463,10 +24864,24 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="4:61" x14ac:dyDescent="0.4">
-      <c r="E36" t="s">
-        <v>22</v>
+    <row r="36" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20" t="s">
+        <v>34</v>
       </c>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
       <c r="AM36">
         <v>45</v>
       </c>
@@ -24480,7 +24895,22 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="4:61" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
       <c r="AN37" s="2"/>
       <c r="AO37" s="2"/>
       <c r="AP37" s="2"/>
@@ -24490,16 +24920,45 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="4:61" x14ac:dyDescent="0.4">
-      <c r="E38" t="s">
+    <row r="38" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20" t="s">
         <v>31</v>
       </c>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="20"/>
+      <c r="P38" s="20"/>
       <c r="AN38" s="2"/>
       <c r="AO38" s="2"/>
       <c r="AP38" s="2"/>
       <c r="AQ38" s="2"/>
     </row>
-    <row r="39" spans="4:61" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
       <c r="AF39" t="s">
         <v>8</v>
       </c>
@@ -24509,16 +24968,37 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="4:61" x14ac:dyDescent="0.4">
-      <c r="E40" t="s">
+    <row r="40" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20" t="s">
         <v>24</v>
       </c>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
       <c r="AN40" s="2"/>
       <c r="BD40">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="4:61" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
       <c r="AM41">
         <v>52</v>
       </c>
@@ -24526,7 +25006,24 @@
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="4:61" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
       <c r="AP42">
         <v>55</v>
       </c>
@@ -24534,10 +25031,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="4:61" x14ac:dyDescent="0.4">
-      <c r="E43" t="s">
-        <v>27</v>
-      </c>
+    <row r="43" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
       <c r="AF43" t="s">
         <v>9</v>
       </c>
@@ -24548,7 +25048,22 @@
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="4:61" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
       <c r="AS44">
         <v>58</v>
       </c>
@@ -24556,7 +25071,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="4:61" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:61" x14ac:dyDescent="0.4">
+      <c r="B45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="20"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
       <c r="AK45">
         <v>57</v>
       </c>
@@ -24564,12 +25087,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="4:61" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:61" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="K46" s="15">
         <v>20</v>
       </c>
       <c r="L46" s="15"/>
-      <c r="M46" s="19">
+      <c r="M46" s="18">
         <v>10</v>
       </c>
       <c r="N46" s="16"/>
@@ -24585,27 +25108,27 @@
       <c r="T46" s="15"/>
       <c r="U46" s="14"/>
       <c r="V46" s="14"/>
-      <c r="W46" s="18">
+      <c r="W46" s="19">
         <v>40</v>
       </c>
-      <c r="X46" s="18"/>
+      <c r="X46" s="19"/>
       <c r="Y46" s="14"/>
       <c r="Z46" s="14"/>
-      <c r="AA46" s="18">
+      <c r="AA46" s="19">
         <v>60</v>
       </c>
-      <c r="AB46" s="18"/>
+      <c r="AB46" s="19"/>
       <c r="AC46" s="14"/>
       <c r="AD46" s="14"/>
-      <c r="AE46" s="18">
+      <c r="AE46" s="19">
         <v>80</v>
       </c>
-      <c r="AF46" s="18"/>
+      <c r="AF46" s="19"/>
       <c r="AW46">
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="4:61" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:61" ht="12.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D47" t="s">
         <v>28</v>
       </c>
